--- a/Inadequate_ID_all_0317_2026.xlsx
+++ b/Inadequate_ID_all_0317_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grace\Box\Luskin Center for Innovation\All Files\Programs\Water\June2015-present\WWNA\Phase 2C\Inadequacy\Population Estimates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71137920-14AF-4C50-AFBC-ABE491D4583E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A06038-5665-47A2-81E4-C1E0AECC1949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="19937" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4834" yWindow="4834" windowWidth="24686" windowHeight="14597" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NPDES" sheetId="1" r:id="rId1"/>
@@ -5126,6 +5126,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{215E31E9-21CA-4CBC-8DEA-6B96E3F54E24}">
   <dimension ref="A1:D161"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3828125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="15" t="s">
@@ -6929,7 +6934,9 @@
       <c r="C129" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D129" s="4"/>
+      <c r="D129" s="4">
+        <v>256442</v>
+      </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A130" s="16">
